--- a/test_parts.xlsx
+++ b/test_parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode-workspace\mura2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AB2E889-6BCC-4EBD-86E4-1E137AC9A4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDB2B9B-9FB1-4ECC-85E7-68049F065999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{AC392815-DF23-40C4-9C3F-BD77DA2F7F9D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC392815-DF23-40C4-9C3F-BD77DA2F7F9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="179">
   <si>
     <t>품번</t>
   </si>
@@ -67,6 +67,510 @@
   </si>
   <si>
     <t>와셔 M6</t>
+  </si>
+  <si>
+    <t>PRT-004</t>
+  </si>
+  <si>
+    <t>와셔 M7</t>
+  </si>
+  <si>
+    <t>스테인리스 305</t>
+  </si>
+  <si>
+    <t>PRT-005</t>
+  </si>
+  <si>
+    <t>와셔 M8</t>
+  </si>
+  <si>
+    <t>스테인리스 306</t>
+  </si>
+  <si>
+    <t>PRT-006</t>
+  </si>
+  <si>
+    <t>와셔 M9</t>
+  </si>
+  <si>
+    <t>스테인리스 307</t>
+  </si>
+  <si>
+    <t>PRT-007</t>
+  </si>
+  <si>
+    <t>와셔 M10</t>
+  </si>
+  <si>
+    <t>스테인리스 308</t>
+  </si>
+  <si>
+    <t>PRT-008</t>
+  </si>
+  <si>
+    <t>와셔 M11</t>
+  </si>
+  <si>
+    <t>스테인리스 309</t>
+  </si>
+  <si>
+    <t>PRT-009</t>
+  </si>
+  <si>
+    <t>와셔 M12</t>
+  </si>
+  <si>
+    <t>스테인리스 310</t>
+  </si>
+  <si>
+    <t>PRT-010</t>
+  </si>
+  <si>
+    <t>와셔 M13</t>
+  </si>
+  <si>
+    <t>스테인리스 311</t>
+  </si>
+  <si>
+    <t>PRT-011</t>
+  </si>
+  <si>
+    <t>와셔 M14</t>
+  </si>
+  <si>
+    <t>스테인리스 312</t>
+  </si>
+  <si>
+    <t>PRT-012</t>
+  </si>
+  <si>
+    <t>와셔 M15</t>
+  </si>
+  <si>
+    <t>스테인리스 313</t>
+  </si>
+  <si>
+    <t>PRT-013</t>
+  </si>
+  <si>
+    <t>와셔 M16</t>
+  </si>
+  <si>
+    <t>스테인리스 314</t>
+  </si>
+  <si>
+    <t>PRT-014</t>
+  </si>
+  <si>
+    <t>와셔 M17</t>
+  </si>
+  <si>
+    <t>스테인리스 315</t>
+  </si>
+  <si>
+    <t>PRT-015</t>
+  </si>
+  <si>
+    <t>와셔 M18</t>
+  </si>
+  <si>
+    <t>스테인리스 316</t>
+  </si>
+  <si>
+    <t>PRT-016</t>
+  </si>
+  <si>
+    <t>와셔 M19</t>
+  </si>
+  <si>
+    <t>스테인리스 317</t>
+  </si>
+  <si>
+    <t>PRT-017</t>
+  </si>
+  <si>
+    <t>와셔 M20</t>
+  </si>
+  <si>
+    <t>스테인리스 318</t>
+  </si>
+  <si>
+    <t>PRT-018</t>
+  </si>
+  <si>
+    <t>와셔 M21</t>
+  </si>
+  <si>
+    <t>스테인리스 319</t>
+  </si>
+  <si>
+    <t>PRT-019</t>
+  </si>
+  <si>
+    <t>와셔 M22</t>
+  </si>
+  <si>
+    <t>스테인리스 320</t>
+  </si>
+  <si>
+    <t>PRT-020</t>
+  </si>
+  <si>
+    <t>와셔 M23</t>
+  </si>
+  <si>
+    <t>스테인리스 321</t>
+  </si>
+  <si>
+    <t>PRT-021</t>
+  </si>
+  <si>
+    <t>와셔 M24</t>
+  </si>
+  <si>
+    <t>스테인리스 322</t>
+  </si>
+  <si>
+    <t>PRT-022</t>
+  </si>
+  <si>
+    <t>와셔 M25</t>
+  </si>
+  <si>
+    <t>스테인리스 323</t>
+  </si>
+  <si>
+    <t>PRT-023</t>
+  </si>
+  <si>
+    <t>와셔 M26</t>
+  </si>
+  <si>
+    <t>스테인리스 324</t>
+  </si>
+  <si>
+    <t>PRT-024</t>
+  </si>
+  <si>
+    <t>와셔 M27</t>
+  </si>
+  <si>
+    <t>스테인리스 325</t>
+  </si>
+  <si>
+    <t>PRT-025</t>
+  </si>
+  <si>
+    <t>와셔 M28</t>
+  </si>
+  <si>
+    <t>스테인리스 326</t>
+  </si>
+  <si>
+    <t>PRT-026</t>
+  </si>
+  <si>
+    <t>와셔 M29</t>
+  </si>
+  <si>
+    <t>스테인리스 327</t>
+  </si>
+  <si>
+    <t>PRT-027</t>
+  </si>
+  <si>
+    <t>와셔 M30</t>
+  </si>
+  <si>
+    <t>스테인리스 328</t>
+  </si>
+  <si>
+    <t>PRT-028</t>
+  </si>
+  <si>
+    <t>와셔 M31</t>
+  </si>
+  <si>
+    <t>스테인리스 329</t>
+  </si>
+  <si>
+    <t>PRT-029</t>
+  </si>
+  <si>
+    <t>와셔 M32</t>
+  </si>
+  <si>
+    <t>스테인리스 330</t>
+  </si>
+  <si>
+    <t>PRT-030</t>
+  </si>
+  <si>
+    <t>와셔 M33</t>
+  </si>
+  <si>
+    <t>스테인리스 331</t>
+  </si>
+  <si>
+    <t>PRT-031</t>
+  </si>
+  <si>
+    <t>와셔 M34</t>
+  </si>
+  <si>
+    <t>스테인리스 332</t>
+  </si>
+  <si>
+    <t>PRT-032</t>
+  </si>
+  <si>
+    <t>와셔 M35</t>
+  </si>
+  <si>
+    <t>스테인리스 333</t>
+  </si>
+  <si>
+    <t>PRT-033</t>
+  </si>
+  <si>
+    <t>와셔 M36</t>
+  </si>
+  <si>
+    <t>스테인리스 334</t>
+  </si>
+  <si>
+    <t>PRT-034</t>
+  </si>
+  <si>
+    <t>와셔 M37</t>
+  </si>
+  <si>
+    <t>스테인리스 335</t>
+  </si>
+  <si>
+    <t>PRT-035</t>
+  </si>
+  <si>
+    <t>와셔 M38</t>
+  </si>
+  <si>
+    <t>스테인리스 336</t>
+  </si>
+  <si>
+    <t>PRT-036</t>
+  </si>
+  <si>
+    <t>와셔 M39</t>
+  </si>
+  <si>
+    <t>스테인리스 337</t>
+  </si>
+  <si>
+    <t>PRT-037</t>
+  </si>
+  <si>
+    <t>와셔 M40</t>
+  </si>
+  <si>
+    <t>스테인리스 338</t>
+  </si>
+  <si>
+    <t>PRT-038</t>
+  </si>
+  <si>
+    <t>와셔 M41</t>
+  </si>
+  <si>
+    <t>스테인리스 339</t>
+  </si>
+  <si>
+    <t>PRT-039</t>
+  </si>
+  <si>
+    <t>와셔 M42</t>
+  </si>
+  <si>
+    <t>스테인리스 340</t>
+  </si>
+  <si>
+    <t>PRT-040</t>
+  </si>
+  <si>
+    <t>와셔 M43</t>
+  </si>
+  <si>
+    <t>스테인리스 341</t>
+  </si>
+  <si>
+    <t>PRT-041</t>
+  </si>
+  <si>
+    <t>와셔 M44</t>
+  </si>
+  <si>
+    <t>스테인리스 342</t>
+  </si>
+  <si>
+    <t>PRT-042</t>
+  </si>
+  <si>
+    <t>와셔 M45</t>
+  </si>
+  <si>
+    <t>스테인리스 343</t>
+  </si>
+  <si>
+    <t>PRT-043</t>
+  </si>
+  <si>
+    <t>와셔 M46</t>
+  </si>
+  <si>
+    <t>스테인리스 344</t>
+  </si>
+  <si>
+    <t>PRT-044</t>
+  </si>
+  <si>
+    <t>와셔 M47</t>
+  </si>
+  <si>
+    <t>스테인리스 345</t>
+  </si>
+  <si>
+    <t>PRT-045</t>
+  </si>
+  <si>
+    <t>와셔 M48</t>
+  </si>
+  <si>
+    <t>스테인리스 346</t>
+  </si>
+  <si>
+    <t>PRT-046</t>
+  </si>
+  <si>
+    <t>와셔 M49</t>
+  </si>
+  <si>
+    <t>스테인리스 347</t>
+  </si>
+  <si>
+    <t>PRT-047</t>
+  </si>
+  <si>
+    <t>와셔 M50</t>
+  </si>
+  <si>
+    <t>스테인리스 348</t>
+  </si>
+  <si>
+    <t>PRT-048</t>
+  </si>
+  <si>
+    <t>와셔 M51</t>
+  </si>
+  <si>
+    <t>스테인리스 349</t>
+  </si>
+  <si>
+    <t>PRT-049</t>
+  </si>
+  <si>
+    <t>와셔 M52</t>
+  </si>
+  <si>
+    <t>스테인리스 350</t>
+  </si>
+  <si>
+    <t>PRT-050</t>
+  </si>
+  <si>
+    <t>와셔 M53</t>
+  </si>
+  <si>
+    <t>스테인리스 351</t>
+  </si>
+  <si>
+    <t>PRT-051</t>
+  </si>
+  <si>
+    <t>와셔 M54</t>
+  </si>
+  <si>
+    <t>스테인리스 352</t>
+  </si>
+  <si>
+    <t>PRT-052</t>
+  </si>
+  <si>
+    <t>와셔 M55</t>
+  </si>
+  <si>
+    <t>스테인리스 353</t>
+  </si>
+  <si>
+    <t>PRT-053</t>
+  </si>
+  <si>
+    <t>와셔 M56</t>
+  </si>
+  <si>
+    <t>스테인리스 354</t>
+  </si>
+  <si>
+    <t>PRT-054</t>
+  </si>
+  <si>
+    <t>와셔 M57</t>
+  </si>
+  <si>
+    <t>스테인리스 355</t>
+  </si>
+  <si>
+    <t>PRT-055</t>
+  </si>
+  <si>
+    <t>와셔 M58</t>
+  </si>
+  <si>
+    <t>스테인리스 356</t>
+  </si>
+  <si>
+    <t>PRT-056</t>
+  </si>
+  <si>
+    <t>와셔 M59</t>
+  </si>
+  <si>
+    <t>스테인리스 357</t>
+  </si>
+  <si>
+    <t>PRT-057</t>
+  </si>
+  <si>
+    <t>와셔 M60</t>
+  </si>
+  <si>
+    <t>스테인리스 358</t>
+  </si>
+  <si>
+    <t>PRT-058</t>
+  </si>
+  <si>
+    <t>와셔 M61</t>
+  </si>
+  <si>
+    <t>스테인리스 359</t>
+  </si>
+  <si>
+    <t>PRT-059</t>
+  </si>
+  <si>
+    <t>와셔 M62</t>
+  </si>
+  <si>
+    <t>스테인리스 360</t>
   </si>
 </sst>
 </file>
@@ -430,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4368B95-F125-458C-8FAD-F1926096A57F}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -489,6 +993,790 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D57">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
